--- a/Tarantula Curve_Mix Design.xlsx
+++ b/Tarantula Curve_Mix Design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ostatemailokstate-my.sharepoint.com/personal/syashin_okstate_edu/Documents/0. LAB documents/project 2/0. Ohio DOT Mix design Submittal process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="8_{A7BFEBA0-CE4E-4E0B-997C-C51F7F717906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B31C0DD-9758-448A-A0D0-E537F53870FB}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="8_{A7BFEBA0-CE4E-4E0B-997C-C51F7F717906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3F3ABA5-A038-5FFA-9DEE-1E56B1677F57}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8935,7 +8935,7 @@
           <c:idx val="4"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Mix 1</c:v>
+            <c:v>Combined Gradation</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="38100">
@@ -9121,7 +9121,7 @@
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
-          <c:order val="2"/>
+          <c:order val="1"/>
           <c:tx>
             <c:v>Maximum Boundary</c:v>
           </c:tx>
@@ -9237,7 +9237,7 @@
         </c:ser>
         <c:ser>
           <c:idx val="8"/>
-          <c:order val="3"/>
+          <c:order val="2"/>
           <c:tx>
             <c:v>Minimum Boundary</c:v>
           </c:tx>
@@ -9428,79 +9428,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Mix 2</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:strRef>
-              <c:f>'Mix Design'!$B$39:$B$50</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>1.5"</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1"</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3/4"</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1/2"</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3/8"</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>#4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>#8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>#16</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>#30</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>#50</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>#100</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>#200</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Mix Design'!$I$39:$I$50</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="12"/>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-3574-4ED7-ABFD-EDBF5DD06139}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
           <c:idx val="7"/>
-          <c:order val="4"/>
+          <c:order val="3"/>
           <c:tx>
             <c:v>Control Fine</c:v>
           </c:tx>
@@ -9553,7 +9482,7 @@
         </c:ser>
         <c:ser>
           <c:idx val="10"/>
-          <c:order val="5"/>
+          <c:order val="4"/>
           <c:tx>
             <c:v>Control C</c:v>
           </c:tx>
@@ -9606,7 +9535,7 @@
         </c:ser>
         <c:ser>
           <c:idx val="0"/>
-          <c:order val="6"/>
+          <c:order val="5"/>
           <c:tx>
             <c:v>Fine Sand Upper Limit</c:v>
           </c:tx>
@@ -9661,7 +9590,7 @@
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
-          <c:order val="7"/>
+          <c:order val="6"/>
           <c:tx>
             <c:v>Fine Sand Lower Limit</c:v>
           </c:tx>
@@ -9789,7 +9718,7 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -9816,6 +9745,10 @@
     <c:legend>
       <c:legendPos val="r"/>
       <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
         <c:idx val="4"/>
         <c:delete val="1"/>
       </c:legendEntry>
@@ -9827,18 +9760,14 @@
         <c:idx val="6"/>
         <c:delete val="1"/>
       </c:legendEntry>
-      <c:legendEntry>
-        <c:idx val="7"/>
-        <c:delete val="1"/>
-      </c:legendEntry>
       <c:layout>
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
           <c:x val="0.70364134409732426"/>
           <c:y val="5.6693507731500219E-2"/>
-          <c:w val="0.24803437912993104"/>
-          <c:h val="0.20112454983585151"/>
+          <c:w val="0.26001985134319283"/>
+          <c:h val="0.14450617803849036"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
